--- a/StructureDefinition-mii-pr-icu-extrakorporales-verfahren.xlsx
+++ b/StructureDefinition-mii-pr-icu-extrakorporales-verfahren.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$148</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="671">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T06:46:19+00:00</t>
+    <t>2026-09-15T22:20:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1284,9 +1284,6 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
-    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
-  </si>
-  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -1868,22 +1865,6 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
-  </si>
-  <si>
-    <t>Procedure.bodySite.extension:bodySite</t>
-  </si>
-  <si>
-    <t>bodySite</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {bodySite}
-</t>
-  </si>
-  <si>
-    <t>Target anatomic location or structure</t>
-  </si>
-  <si>
-    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2438,7 +2419,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM149"/>
+  <dimension ref="A1:AM148"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4682,7 +4663,7 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>112</v>
@@ -4902,7 +4883,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
@@ -9336,7 +9317,7 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>112</v>
@@ -9667,7 +9648,7 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>112</v>
@@ -9885,7 +9866,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -10105,7 +10086,7 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>112</v>
@@ -10218,7 +10199,7 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
@@ -10329,7 +10310,7 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>96</v>
@@ -10380,9 +10361,7 @@
       <c r="M72" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N72" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
         <v>243</v>
       </c>
@@ -10442,7 +10421,7 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>96</v>
@@ -10459,10 +10438,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="B73" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="B73" t="s" s="2">
-        <v>409</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10493,9 +10472,7 @@
       <c r="M73" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N73" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
         <v>250</v>
       </c>
@@ -10555,7 +10532,7 @@
         <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>96</v>
@@ -10572,10 +10549,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="B74" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10668,7 +10645,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -10685,10 +10662,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="B75" t="s" s="2">
         <v>412</v>
-      </c>
-      <c r="B75" t="s" s="2">
-        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10714,7 +10691,7 @@
         <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>226</v>
@@ -10730,7 +10707,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -10781,7 +10758,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
@@ -10798,10 +10775,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="B76" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="B76" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10827,10 +10804,10 @@
         <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="M76" t="s" s="2">
         <v>418</v>
-      </c>
-      <c r="M76" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>236</v>
@@ -10892,7 +10869,7 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>96</v>
@@ -10909,10 +10886,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="B77" t="s" s="2">
         <v>420</v>
-      </c>
-      <c r="B77" t="s" s="2">
-        <v>421</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10938,14 +10915,12 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N77" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N77" s="2"/>
       <c r="O77" t="s" s="2">
         <v>243</v>
       </c>
@@ -10960,7 +10935,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -11005,10 +10980,10 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -11022,10 +10997,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="B78" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="B78" t="s" s="2">
-        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11056,9 +11031,7 @@
       <c r="M78" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N78" t="s" s="2">
-        <v>407</v>
-      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
         <v>250</v>
       </c>
@@ -11118,7 +11091,7 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>96</v>
@@ -11135,10 +11108,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="B79" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="B79" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11231,7 +11204,7 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>189</v>
+        <v>75</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>96</v>
@@ -11248,7 +11221,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>370</v>
@@ -11298,7 +11271,7 @@
         <v>75</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>75</v>
@@ -11316,10 +11289,10 @@
         <v>217</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>431</v>
-      </c>
-      <c r="Z80" t="s" s="2">
-        <v>432</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11363,7 +11336,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>379</v>
@@ -11472,7 +11445,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>381</v>
@@ -11583,10 +11556,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11696,10 +11669,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11807,10 +11780,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11918,10 +11891,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12029,10 +12002,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12142,10 +12115,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12255,14 +12228,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12281,13 +12254,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="L89" t="s" s="2">
+      <c r="M89" t="s" s="2">
         <v>444</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>445</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12338,7 +12311,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>84</v>
@@ -12353,21 +12326,21 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AL89" t="s" s="2">
         <v>446</v>
       </c>
-      <c r="AL89" t="s" s="2">
+      <c r="AM89" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>448</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12473,10 +12446,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12584,10 +12557,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12613,13 +12586,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N92" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12669,16 +12642,16 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI92" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AG92" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH92" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI92" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>96</v>
@@ -12695,10 +12668,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12724,13 +12697,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12759,28 +12732,28 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z93" t="s" s="2">
+      <c r="AA93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF93" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AA93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE93" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF93" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12806,10 +12779,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12835,13 +12808,13 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M94" t="s" s="2">
+      <c r="N94" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N94" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12891,7 +12864,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12917,10 +12890,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12946,13 +12919,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M95" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M95" t="s" s="2">
+      <c r="N95" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13002,7 +12975,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13028,10 +13001,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13054,16 +13027,16 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="L96" t="s" s="2">
         <v>475</v>
       </c>
-      <c r="L96" t="s" s="2">
+      <c r="M96" t="s" s="2">
         <v>476</v>
       </c>
-      <c r="M96" t="s" s="2">
+      <c r="N96" t="s" s="2">
         <v>477</v>
-      </c>
-      <c r="N96" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13113,7 +13086,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13128,21 +13101,21 @@
         <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL96" t="s" s="2">
         <v>479</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AM96" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="AM96" t="s" s="2">
-        <v>481</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13248,10 +13221,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13359,10 +13332,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13388,13 +13361,13 @@
         <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M99" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="M99" t="s" s="2">
+      <c r="N99" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="N99" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13444,16 +13417,16 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI99" t="s" s="2">
         <v>455</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>456</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>96</v>
@@ -13470,10 +13443,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13499,13 +13472,13 @@
         <v>125</v>
       </c>
       <c r="L100" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="M100" t="s" s="2">
         <v>458</v>
       </c>
-      <c r="M100" t="s" s="2">
+      <c r="N100" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13534,28 +13507,28 @@
         <v>141</v>
       </c>
       <c r="Y100" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Z100" t="s" s="2">
         <v>461</v>
       </c>
-      <c r="Z100" t="s" s="2">
+      <c r="AA100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF100" t="s" s="2">
         <v>462</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>463</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13581,10 +13554,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13610,13 +13583,13 @@
         <v>268</v>
       </c>
       <c r="L101" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M101" t="s" s="2">
         <v>465</v>
       </c>
-      <c r="M101" t="s" s="2">
+      <c r="N101" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="N101" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13666,7 +13639,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13692,10 +13665,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13721,13 +13694,13 @@
         <v>98</v>
       </c>
       <c r="L102" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M102" t="s" s="2">
         <v>470</v>
       </c>
-      <c r="M102" t="s" s="2">
+      <c r="N102" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13777,7 +13750,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13803,10 +13776,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13829,16 +13802,16 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="L103" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="L103" t="s" s="2">
+      <c r="M103" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="M103" t="s" s="2">
+      <c r="N103" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13876,17 +13849,17 @@
         <v>75</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13901,21 +13874,21 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL103" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AL103" t="s" s="2">
+      <c r="AM103" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14021,10 +13994,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14132,10 +14105,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14161,13 +14134,13 @@
         <v>203</v>
       </c>
       <c r="L106" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M106" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M106" t="s" s="2">
+      <c r="N106" t="s" s="2">
         <v>502</v>
-      </c>
-      <c r="N106" t="s" s="2">
-        <v>503</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14217,16 +14190,16 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI106" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>96</v>
@@ -14238,15 +14211,15 @@
         <v>75</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14272,66 +14245,66 @@
         <v>203</v>
       </c>
       <c r="L107" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="M107" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="M107" t="s" s="2">
+      <c r="N107" t="s" s="2">
         <v>509</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q107" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="R107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF107" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="R107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>512</v>
-      </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
       </c>
@@ -14339,7 +14312,7 @@
         <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>96</v>
@@ -14351,18 +14324,18 @@
         <v>75</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C108" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C108" t="s" s="2">
-        <v>515</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>75</v>
@@ -14387,13 +14360,13 @@
         <v>203</v>
       </c>
       <c r="L108" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="M108" t="s" s="2">
         <v>516</v>
       </c>
-      <c r="M108" t="s" s="2">
-        <v>517</v>
-      </c>
       <c r="N108" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14443,7 +14416,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14458,24 +14431,24 @@
         <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL108" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AL108" t="s" s="2">
+      <c r="AM108" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="C109" t="s" s="2">
         <v>518</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>488</v>
-      </c>
-      <c r="C109" t="s" s="2">
-        <v>519</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>75</v>
@@ -14497,16 +14470,16 @@
         <v>85</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="L109" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M109" t="s" s="2">
         <v>520</v>
       </c>
-      <c r="M109" t="s" s="2">
-        <v>521</v>
-      </c>
       <c r="N109" t="s" s="2">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14556,7 +14529,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14571,21 +14544,21 @@
         <v>96</v>
       </c>
       <c r="AK109" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="AL109" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="AL109" t="s" s="2">
+      <c r="AM109" t="s" s="2">
         <v>496</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>497</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14608,13 +14581,13 @@
         <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="L110" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="L110" t="s" s="2">
+      <c r="M110" t="s" s="2">
         <v>524</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>525</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14665,7 +14638,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14683,7 +14656,7 @@
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14691,10 +14664,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14717,13 +14690,13 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="L111" t="s" s="2">
         <v>528</v>
       </c>
-      <c r="L111" t="s" s="2">
+      <c r="M111" t="s" s="2">
         <v>529</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>530</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14774,7 +14747,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14792,7 +14765,7 @@
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>75</v>
@@ -14800,10 +14773,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14826,13 +14799,13 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L112" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="L112" t="s" s="2">
+      <c r="M112" t="s" s="2">
         <v>534</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>535</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14883,7 +14856,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14898,7 +14871,7 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>75</v>
@@ -14909,10 +14882,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15018,10 +14991,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15129,14 +15102,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15158,10 +15131,10 @@
         <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M115" t="s" s="2">
         <v>541</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>542</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>107</v>
@@ -15216,7 +15189,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15242,10 +15215,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15271,14 +15244,14 @@
         <v>308</v>
       </c>
       <c r="L116" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="M116" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>75</v>
@@ -15306,11 +15279,11 @@
         <v>149</v>
       </c>
       <c r="Y116" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="Z116" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="Z116" t="s" s="2">
-        <v>549</v>
-      </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
       </c>
@@ -15327,7 +15300,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15342,21 +15315,21 @@
         <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM116" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>551</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15379,17 +15352,17 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="L117" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="L117" t="s" s="2">
+      <c r="M117" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>555</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -15438,7 +15411,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -15453,21 +15426,21 @@
         <v>96</v>
       </c>
       <c r="AK117" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="AL117" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AL117" t="s" s="2">
+      <c r="AM117" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>559</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15490,17 +15463,17 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="L118" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="L118" t="s" s="2">
+      <c r="M118" t="s" s="2">
         <v>562</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>563</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15549,7 +15522,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15575,10 +15548,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15601,17 +15574,17 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L119" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L119" t="s" s="2">
+      <c r="M119" t="s" s="2">
         <v>567</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>568</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -15660,7 +15633,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15678,7 +15651,7 @@
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>75</v>
@@ -15686,10 +15659,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15715,13 +15688,13 @@
         <v>308</v>
       </c>
       <c r="L120" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="M120" t="s" s="2">
         <v>572</v>
       </c>
-      <c r="M120" t="s" s="2">
+      <c r="N120" t="s" s="2">
         <v>573</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>574</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15750,11 +15723,11 @@
         <v>149</v>
       </c>
       <c r="Y120" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="Z120" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="Z120" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
       </c>
@@ -15771,7 +15744,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15786,10 +15759,10 @@
         <v>96</v>
       </c>
       <c r="AK120" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AL120" t="s" s="2">
         <v>577</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>578</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>75</v>
@@ -15797,10 +15770,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15823,16 +15796,16 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="L121" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="L121" t="s" s="2">
+      <c r="M121" t="s" s="2">
         <v>581</v>
       </c>
-      <c r="M121" t="s" s="2">
+      <c r="N121" t="s" s="2">
         <v>582</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>583</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -15882,7 +15855,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15897,10 +15870,10 @@
         <v>96</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>75</v>
@@ -15908,10 +15881,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15937,13 +15910,13 @@
         <v>308</v>
       </c>
       <c r="L122" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="M122" t="s" s="2">
         <v>586</v>
       </c>
-      <c r="M122" t="s" s="2">
+      <c r="N122" t="s" s="2">
         <v>587</v>
-      </c>
-      <c r="N122" t="s" s="2">
-        <v>588</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15972,11 +15945,11 @@
         <v>149</v>
       </c>
       <c r="Y122" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="Z122" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="Z122" t="s" s="2">
-        <v>590</v>
-      </c>
       <c r="AA122" t="s" s="2">
         <v>75</v>
       </c>
@@ -15993,7 +15966,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16014,15 +15987,15 @@
         <v>75</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16128,10 +16101,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16239,14 +16212,12 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="C125" t="s" s="2">
-        <v>595</v>
-      </c>
+      <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16255,28 +16226,32 @@
         <v>76</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>596</v>
+        <v>137</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>597</v>
+        <v>324</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
+        <v>325</v>
+      </c>
+      <c r="N125" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O125" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16312,19 +16287,17 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>594</v>
+      </c>
+      <c r="AC125" s="2"/>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>111</v>
+        <v>329</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16336,7 +16309,7 @@
         <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
@@ -16345,17 +16318,19 @@
         <v>75</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
     </row>
-    <row r="126" hidden="true">
+    <row r="126">
       <c r="A126" t="s" s="2">
-        <v>599</v>
+        <v>595</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C126" s="2"/>
+        <v>593</v>
+      </c>
+      <c r="C126" t="s" s="2">
+        <v>596</v>
+      </c>
       <c r="D126" t="s" s="2">
         <v>75</v>
       </c>
@@ -16364,7 +16339,7 @@
         <v>76</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>85</v>
@@ -16379,10 +16354,10 @@
         <v>137</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>326</v>
@@ -16425,14 +16400,16 @@
         <v>75</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AC126" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC126" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
         <v>329</v>
@@ -16459,16 +16436,14 @@
         <v>330</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>601</v>
+        <v>597</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="C127" t="s" s="2">
-        <v>602</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16480,29 +16455,25 @@
         <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>137</v>
+        <v>98</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>333</v>
+        <v>99</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N127" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O127" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16550,19 +16521,19 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>329</v>
+        <v>101</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -16571,26 +16542,26 @@
         <v>75</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>603</v>
+        <v>599</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>75</v>
@@ -16602,15 +16573,17 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N128" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N128" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -16647,31 +16620,31 @@
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -16683,46 +16656,48 @@
         <v>75</v>
       </c>
     </row>
-    <row r="129" hidden="true">
+    <row r="129">
       <c r="A129" t="s" s="2">
-        <v>605</v>
+        <v>601</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>606</v>
+        <v>602</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>104</v>
+        <v>125</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>105</v>
+        <v>225</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>106</v>
+        <v>226</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O129" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O129" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -16731,7 +16706,7 @@
         <v>75</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>75</v>
@@ -16758,31 +16733,31 @@
         <v>75</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>111</v>
+        <v>230</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -16791,15 +16766,15 @@
         <v>75</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>75</v>
+        <v>231</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>607</v>
+        <v>603</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>608</v>
+        <v>604</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16807,7 +16782,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>84</v>
@@ -16822,20 +16797,18 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>125</v>
+        <v>98</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O130" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="O130" s="2"/>
       <c r="P130" t="s" s="2">
         <v>75</v>
       </c>
@@ -16844,7 +16817,7 @@
         <v>75</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>75</v>
@@ -16883,7 +16856,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16904,15 +16877,15 @@
         <v>75</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>231</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>609</v>
+        <v>605</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>610</v>
+        <v>606</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16920,7 +16893,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>84</v>
@@ -16935,18 +16908,18 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>235</v>
-      </c>
-      <c r="N131" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O131" s="2"/>
+        <v>242</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" t="s" s="2">
+        <v>243</v>
+      </c>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16994,7 +16967,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17015,15 +16988,15 @@
         <v>75</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>238</v>
+        <v>245</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>611</v>
+        <v>607</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>612</v>
+        <v>608</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17031,13 +17004,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>75</v>
@@ -17046,17 +17019,17 @@
         <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>75</v>
@@ -17105,7 +17078,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17126,15 +17099,15 @@
         <v>75</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>613</v>
+        <v>609</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17157,17 +17130,19 @@
         <v>85</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="N133" s="2"/>
+        <v>257</v>
+      </c>
+      <c r="N133" t="s" s="2">
+        <v>258</v>
+      </c>
       <c r="O133" t="s" s="2">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>75</v>
@@ -17216,7 +17191,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17237,15 +17212,15 @@
         <v>75</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>615</v>
+        <v>611</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>616</v>
+        <v>611</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17268,19 +17243,19 @@
         <v>85</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>256</v>
+        <v>352</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>257</v>
+        <v>353</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>258</v>
+        <v>354</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>259</v>
+        <v>355</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -17329,7 +17304,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>260</v>
+        <v>356</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17350,15 +17325,15 @@
         <v>75</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>261</v>
+        <v>357</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>617</v>
+        <v>612</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17381,20 +17356,18 @@
         <v>85</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>98</v>
+        <v>308</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>352</v>
+        <v>613</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>353</v>
+        <v>614</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="O135" t="s" s="2">
-        <v>355</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="O135" s="2"/>
       <c r="P135" t="s" s="2">
         <v>75</v>
       </c>
@@ -17418,13 +17391,13 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>75</v>
+        <v>616</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>75</v>
+        <v>617</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -17442,7 +17415,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>356</v>
+        <v>612</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17463,7 +17436,7 @@
         <v>75</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
     </row>
     <row r="136" hidden="true">
@@ -17482,7 +17455,7 @@
         <v>76</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>75</v>
@@ -17491,19 +17464,19 @@
         <v>75</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>308</v>
+        <v>619</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N136" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17529,13 +17502,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>622</v>
+        <v>75</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>623</v>
+        <v>75</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -17559,7 +17532,7 @@
         <v>76</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>75</v>
@@ -17579,10 +17552,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17605,16 +17578,16 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L137" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="M137" t="s" s="2">
         <v>625</v>
       </c>
-      <c r="L137" t="s" s="2">
+      <c r="N137" t="s" s="2">
         <v>626</v>
-      </c>
-      <c r="M137" t="s" s="2">
-        <v>627</v>
-      </c>
-      <c r="N137" t="s" s="2">
-        <v>628</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17640,13 +17613,13 @@
         <v>75</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>75</v>
+        <v>627</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>75</v>
+        <v>628</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>75</v>
@@ -17664,7 +17637,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -17716,18 +17689,18 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>308</v>
+        <v>630</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>631</v>
-      </c>
-      <c r="N138" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="O138" s="2"/>
+      <c r="N138" s="2"/>
+      <c r="O138" t="s" s="2">
+        <v>633</v>
+      </c>
       <c r="P138" t="s" s="2">
         <v>75</v>
       </c>
@@ -17751,13 +17724,13 @@
         <v>75</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>633</v>
+        <v>75</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>634</v>
+        <v>75</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
@@ -17801,10 +17774,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17827,18 +17800,16 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L139" t="s" s="2">
+        <v>635</v>
+      </c>
+      <c r="M139" t="s" s="2">
         <v>636</v>
       </c>
-      <c r="L139" t="s" s="2">
-        <v>637</v>
-      </c>
-      <c r="M139" t="s" s="2">
-        <v>638</v>
-      </c>
       <c r="N139" s="2"/>
-      <c r="O139" t="s" s="2">
-        <v>639</v>
-      </c>
+      <c r="O139" s="2"/>
       <c r="P139" t="s" s="2">
         <v>75</v>
       </c>
@@ -17862,13 +17833,13 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>75</v>
+        <v>637</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>75</v>
+        <v>638</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>75</v>
@@ -17886,7 +17857,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17910,12 +17881,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140" hidden="true">
+    <row r="140">
       <c r="A140" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17929,7 +17900,7 @@
         <v>77</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>75</v>
@@ -17938,7 +17909,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>308</v>
+        <v>640</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>641</v>
@@ -17971,13 +17942,13 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>643</v>
+        <v>75</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>644</v>
+        <v>75</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -17995,7 +17966,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18010,16 +17981,16 @@
         <v>96</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>75</v>
+        <v>644</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
         <v>645</v>
       </c>
@@ -18038,7 +18009,7 @@
         <v>77</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>75</v>
@@ -18047,13 +18018,13 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="L141" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="L141" t="s" s="2">
+      <c r="M141" t="s" s="2">
         <v>647</v>
-      </c>
-      <c r="M141" t="s" s="2">
-        <v>648</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18119,21 +18090,21 @@
         <v>96</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>649</v>
+        <v>75</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>650</v>
+        <v>75</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18144,7 +18115,7 @@
         <v>76</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>75</v>
@@ -18156,13 +18127,13 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>533</v>
+        <v>98</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>652</v>
+        <v>99</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>653</v>
+        <v>100</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18213,19 +18184,19 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>651</v>
+        <v>101</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>75</v>
@@ -18239,21 +18210,21 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>654</v>
+        <v>649</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -18265,15 +18236,17 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N143" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="N143" t="s" s="2">
+        <v>107</v>
+      </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>75</v>
@@ -18322,19 +18295,19 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>75</v>
@@ -18348,14 +18321,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>655</v>
+        <v>650</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>103</v>
+        <v>539</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18368,24 +18341,26 @@
         <v>75</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>105</v>
+        <v>540</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>106</v>
+        <v>541</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O144" s="2"/>
+      <c r="O144" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P144" t="s" s="2">
         <v>75</v>
       </c>
@@ -18433,7 +18408,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>111</v>
+        <v>542</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18459,46 +18434,42 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>651</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>540</v>
+        <v>75</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>104</v>
+        <v>308</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>541</v>
+        <v>652</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N145" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="O145" t="s" s="2">
-        <v>265</v>
-      </c>
+        <v>653</v>
+      </c>
+      <c r="N145" s="2"/>
+      <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
         <v>75</v>
       </c>
@@ -18522,13 +18493,13 @@
         <v>75</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>75</v>
+        <v>654</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>75</v>
+        <v>655</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>75</v>
@@ -18546,19 +18517,19 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>543</v>
+        <v>651</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -18572,10 +18543,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18583,7 +18554,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>84</v>
@@ -18598,7 +18569,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>308</v>
+        <v>657</v>
       </c>
       <c r="L146" t="s" s="2">
         <v>658</v>
@@ -18631,13 +18602,13 @@
         <v>75</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>660</v>
+        <v>75</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>661</v>
+        <v>75</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>75</v>
@@ -18655,10 +18626,10 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>84</v>
@@ -18681,10 +18652,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18692,10 +18663,10 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>75</v>
@@ -18707,16 +18678,20 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="L147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>664</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="O147" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="N147" s="2"/>
-      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>75</v>
       </c>
@@ -18764,13 +18739,13 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>75</v>
@@ -18816,20 +18791,18 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L148" t="s" s="2">
         <v>667</v>
       </c>
-      <c r="L148" t="s" s="2">
+      <c r="M148" t="s" s="2">
         <v>668</v>
       </c>
-      <c r="M148" t="s" s="2">
-        <v>669</v>
-      </c>
       <c r="N148" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O148" t="s" s="2">
-        <v>671</v>
-      </c>
+        <v>664</v>
+      </c>
+      <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
         <v>75</v>
       </c>
@@ -18853,13 +18826,13 @@
         <v>75</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>75</v>
+        <v>669</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>75</v>
+        <v>670</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>75</v>
@@ -18901,119 +18874,8 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149" hidden="true">
-      <c r="A149" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="B149" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="C149" s="2"/>
-      <c r="D149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E149" s="2"/>
-      <c r="F149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G149" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="H149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K149" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>673</v>
-      </c>
-      <c r="M149" t="s" s="2">
-        <v>674</v>
-      </c>
-      <c r="N149" t="s" s="2">
-        <v>670</v>
-      </c>
-      <c r="O149" s="2"/>
-      <c r="P149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q149" s="2"/>
-      <c r="R149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X149" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y149" t="s" s="2">
-        <v>675</v>
-      </c>
-      <c r="Z149" t="s" s="2">
-        <v>676</v>
-      </c>
-      <c r="AA149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF149" t="s" s="2">
-        <v>672</v>
-      </c>
-      <c r="AG149" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH149" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AI149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ149" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AK149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AL149" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AM149" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AM149">
+  <autoFilter ref="A1:AM148">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -19023,7 +18885,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI148">
+  <conditionalFormatting sqref="A2:AI147">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/StructureDefinition-mii-pr-icu-extrakorporales-verfahren.xlsx
+++ b/StructureDefinition-mii-pr-icu-extrakorporales-verfahren.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$149</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5208" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5247" uniqueCount="677">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T22:20:02+00:00</t>
+    <t>2026-09-17T12:17:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1284,6 +1284,9 @@
     <t>Procedure.code.coding.extension.value[x].code</t>
   </si>
   <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
+  </si>
+  <si>
     <t>Procedure.code.coding:ops.extension:Seitenlokalisation.value[x].display</t>
   </si>
   <si>
@@ -1865,6 +1868,22 @@
   </si>
   <si>
     <t>Procedure.bodySite.extension</t>
+  </si>
+  <si>
+    <t>Procedure.bodySite.extension:bodySite</t>
+  </si>
+  <si>
+    <t>bodySite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {bodySite}
+</t>
+  </si>
+  <si>
+    <t>Target anatomic location or structure</t>
+  </si>
+  <si>
+    <t>Record details about the anatomical location of a specimen or body part. This resource may be used when a coded concept does not provide the necessary detail needed for the use case.</t>
   </si>
   <si>
     <t>Procedure.bodySite.coding</t>
@@ -2419,7 +2438,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AM148"/>
+  <dimension ref="A1:AM149"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="62.5703125" customWidth="true" bestFit="true"/>
@@ -4663,7 +4682,7 @@
         <v>77</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>112</v>
@@ -4883,7 +4902,7 @@
         <v>84</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>96</v>
@@ -9317,7 +9336,7 @@
         <v>77</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ62" t="s" s="2">
         <v>112</v>
@@ -9648,7 +9667,7 @@
         <v>77</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>112</v>
@@ -9866,7 +9885,7 @@
         <v>84</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>96</v>
@@ -10086,7 +10105,7 @@
         <v>77</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>112</v>
@@ -10199,7 +10218,7 @@
         <v>84</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ70" t="s" s="2">
         <v>96</v>
@@ -10310,7 +10329,7 @@
         <v>84</v>
       </c>
       <c r="AI71" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ71" t="s" s="2">
         <v>96</v>
@@ -10361,7 +10380,9 @@
       <c r="M72" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N72" s="2"/>
+      <c r="N72" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O72" t="s" s="2">
         <v>243</v>
       </c>
@@ -10421,7 +10442,7 @@
         <v>84</v>
       </c>
       <c r="AI72" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ72" t="s" s="2">
         <v>96</v>
@@ -10438,10 +10459,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10472,7 +10493,9 @@
       <c r="M73" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N73" s="2"/>
+      <c r="N73" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O73" t="s" s="2">
         <v>250</v>
       </c>
@@ -10532,7 +10555,7 @@
         <v>84</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>96</v>
@@ -10549,10 +10572,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10645,7 +10668,7 @@
         <v>84</v>
       </c>
       <c r="AI74" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ74" t="s" s="2">
         <v>96</v>
@@ -10662,10 +10685,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10691,7 +10714,7 @@
         <v>125</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M75" t="s" s="2">
         <v>226</v>
@@ -10707,7 +10730,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -10758,7 +10781,7 @@
         <v>84</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>96</v>
@@ -10775,10 +10798,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10804,10 +10827,10 @@
         <v>98</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>236</v>
@@ -10869,7 +10892,7 @@
         <v>84</v>
       </c>
       <c r="AI76" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ76" t="s" s="2">
         <v>96</v>
@@ -10886,10 +10909,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10915,12 +10938,14 @@
         <v>159</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M77" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="N77" s="2"/>
+      <c r="N77" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O77" t="s" s="2">
         <v>243</v>
       </c>
@@ -10935,7 +10960,7 @@
         <v>75</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>75</v>
@@ -10980,10 +11005,10 @@
         <v>84</v>
       </c>
       <c r="AI77" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AK77" t="s" s="2">
         <v>75</v>
@@ -10997,10 +11022,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11031,7 +11056,9 @@
       <c r="M78" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="N78" s="2"/>
+      <c r="N78" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O78" t="s" s="2">
         <v>250</v>
       </c>
@@ -11091,7 +11118,7 @@
         <v>84</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>96</v>
@@ -11108,10 +11135,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11204,7 +11231,7 @@
         <v>84</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>75</v>
+        <v>189</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>96</v>
@@ -11221,7 +11248,7 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>370</v>
@@ -11271,7 +11298,7 @@
         <v>75</v>
       </c>
       <c r="S80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="T80" t="s" s="2">
         <v>75</v>
@@ -11289,10 +11316,10 @@
         <v>217</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>75</v>
@@ -11336,7 +11363,7 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s" s="2">
         <v>379</v>
@@ -11445,7 +11472,7 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B82" t="s" s="2">
         <v>381</v>
@@ -11556,10 +11583,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11669,10 +11696,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11780,10 +11807,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11891,10 +11918,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12002,10 +12029,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12115,10 +12142,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12228,14 +12255,14 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -12254,13 +12281,13 @@
         <v>85</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12311,7 +12338,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>84</v>
@@ -12326,21 +12353,21 @@
         <v>96</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12446,10 +12473,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12557,10 +12584,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12586,13 +12613,13 @@
         <v>98</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -12642,7 +12669,7 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -12651,7 +12678,7 @@
         <v>84</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>96</v>
@@ -12668,10 +12695,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12697,13 +12724,13 @@
         <v>125</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -12732,10 +12759,10 @@
         <v>141</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>75</v>
@@ -12753,7 +12780,7 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -12779,10 +12806,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12808,13 +12835,13 @@
         <v>268</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12864,7 +12891,7 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>76</v>
@@ -12890,10 +12917,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12919,13 +12946,13 @@
         <v>98</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12975,7 +13002,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13001,10 +13028,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13027,16 +13054,16 @@
         <v>85</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13086,7 +13113,7 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13101,21 +13128,21 @@
         <v>96</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13221,10 +13248,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13332,10 +13359,10 @@
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13361,13 +13388,13 @@
         <v>98</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13417,7 +13444,7 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13426,7 +13453,7 @@
         <v>84</v>
       </c>
       <c r="AI99" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AJ99" t="s" s="2">
         <v>96</v>
@@ -13443,10 +13470,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13472,13 +13499,13 @@
         <v>125</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -13507,10 +13534,10 @@
         <v>141</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -13528,7 +13555,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>76</v>
@@ -13554,10 +13581,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13583,13 +13610,13 @@
         <v>268</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13639,7 +13666,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>76</v>
@@ -13665,10 +13692,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13694,13 +13721,13 @@
         <v>98</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13750,7 +13777,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -13776,10 +13803,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13802,16 +13829,16 @@
         <v>85</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13849,17 +13876,17 @@
         <v>75</v>
       </c>
       <c r="AB103" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AC103" s="2"/>
       <c r="AD103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE103" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>76</v>
@@ -13874,21 +13901,21 @@
         <v>96</v>
       </c>
       <c r="AK103" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13994,10 +14021,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14105,10 +14132,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14134,13 +14161,13 @@
         <v>203</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14190,7 +14217,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14199,7 +14226,7 @@
         <v>84</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>96</v>
@@ -14211,15 +14238,15 @@
         <v>75</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14245,20 +14272,20 @@
         <v>203</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="Q107" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="R107" t="s" s="2">
         <v>75</v>
@@ -14303,7 +14330,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14312,7 +14339,7 @@
         <v>84</v>
       </c>
       <c r="AI107" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="AJ107" t="s" s="2">
         <v>96</v>
@@ -14324,18 +14351,18 @@
         <v>75</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C108" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="D108" t="s" s="2">
         <v>75</v>
@@ -14360,13 +14387,13 @@
         <v>203</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14416,7 +14443,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14431,24 +14458,24 @@
         <v>96</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C109" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="D109" t="s" s="2">
         <v>75</v>
@@ -14470,16 +14497,16 @@
         <v>85</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14529,7 +14556,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14544,21 +14571,21 @@
         <v>96</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14581,13 +14608,13 @@
         <v>85</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -14638,7 +14665,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -14656,7 +14683,7 @@
         <v>75</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>75</v>
@@ -14664,10 +14691,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14690,13 +14717,13 @@
         <v>85</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -14747,7 +14774,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>76</v>
@@ -14765,7 +14792,7 @@
         <v>75</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>75</v>
@@ -14773,10 +14800,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14799,13 +14826,13 @@
         <v>85</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14856,7 +14883,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -14871,7 +14898,7 @@
         <v>96</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AL112" t="s" s="2">
         <v>75</v>
@@ -14882,10 +14909,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14991,10 +15018,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15102,14 +15129,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -15131,10 +15158,10 @@
         <v>104</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="N115" t="s" s="2">
         <v>107</v>
@@ -15189,7 +15216,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15215,10 +15242,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15244,14 +15271,14 @@
         <v>308</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>75</v>
@@ -15279,10 +15306,10 @@
         <v>149</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -15300,7 +15327,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15315,21 +15342,21 @@
         <v>96</v>
       </c>
       <c r="AK116" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AL116" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15352,17 +15379,17 @@
         <v>85</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>75</v>
@@ -15411,7 +15438,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>84</v>
@@ -15426,21 +15453,21 @@
         <v>96</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -15463,17 +15490,17 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>75</v>
@@ -15522,7 +15549,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15548,10 +15575,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15574,17 +15601,17 @@
         <v>85</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>75</v>
@@ -15633,7 +15660,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>76</v>
@@ -15651,7 +15678,7 @@
         <v>75</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>75</v>
@@ -15659,10 +15686,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15688,13 +15715,13 @@
         <v>308</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -15723,10 +15750,10 @@
         <v>149</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>75</v>
@@ -15744,7 +15771,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -15759,10 +15786,10 @@
         <v>96</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>75</v>
@@ -15770,10 +15797,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15796,16 +15823,16 @@
         <v>85</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -15855,7 +15882,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -15870,10 +15897,10 @@
         <v>96</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>75</v>
@@ -15881,10 +15908,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15910,13 +15937,13 @@
         <v>308</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -15945,10 +15972,10 @@
         <v>149</v>
       </c>
       <c r="Y122" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="Z122" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="AA122" t="s" s="2">
         <v>75</v>
@@ -15966,7 +15993,7 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -15987,15 +16014,15 @@
         <v>75</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16101,10 +16128,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16212,12 +16239,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B125" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="C125" s="2"/>
+      <c r="C125" t="s" s="2">
+        <v>595</v>
+      </c>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16226,32 +16255,28 @@
         <v>76</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J125" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>137</v>
+        <v>596</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>324</v>
+        <v>597</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>598</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>75</v>
       </c>
@@ -16287,17 +16312,19 @@
         <v>75</v>
       </c>
       <c r="AB125" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="AC125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD125" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE125" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>329</v>
+        <v>111</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16309,7 +16336,7 @@
         <v>75</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>75</v>
@@ -16318,19 +16345,17 @@
         <v>75</v>
       </c>
       <c r="AM125" t="s" s="2">
-        <v>330</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="C126" t="s" s="2">
-        <v>596</v>
-      </c>
+        <v>599</v>
+      </c>
+      <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
         <v>75</v>
       </c>
@@ -16339,7 +16364,7 @@
         <v>76</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>85</v>
@@ -16354,10 +16379,10 @@
         <v>137</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>334</v>
+        <v>325</v>
       </c>
       <c r="N126" t="s" s="2">
         <v>326</v>
@@ -16400,16 +16425,14 @@
         <v>75</v>
       </c>
       <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="AC126" s="2"/>
       <c r="AD126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE126" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF126" t="s" s="2">
         <v>329</v>
@@ -16436,14 +16459,16 @@
         <v>330</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="C127" s="2"/>
+        <v>599</v>
+      </c>
+      <c r="C127" t="s" s="2">
+        <v>602</v>
+      </c>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16455,25 +16480,29 @@
         <v>84</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J127" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>98</v>
+        <v>137</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>99</v>
+        <v>333</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N127" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="O127" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="P127" t="s" s="2">
         <v>75</v>
       </c>
@@ -16521,19 +16550,19 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH127" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI127" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -16542,26 +16571,26 @@
         <v>75</v>
       </c>
       <c r="AM127" t="s" s="2">
-        <v>75</v>
+        <v>330</v>
       </c>
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H128" t="s" s="2">
         <v>75</v>
@@ -16573,17 +16602,15 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N128" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N128" s="2"/>
       <c r="O128" s="2"/>
       <c r="P128" t="s" s="2">
         <v>75</v>
@@ -16620,31 +16647,31 @@
         <v>75</v>
       </c>
       <c r="AB128" t="s" s="2">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="AC128" t="s" s="2">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="AD128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE128" t="s" s="2">
-        <v>110</v>
+        <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH128" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ128" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AK128" t="s" s="2">
         <v>75</v>
@@ -16656,48 +16683,46 @@
         <v>75</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="E129" s="2"/>
       <c r="F129" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H129" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J129" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>125</v>
+        <v>104</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>225</v>
+        <v>105</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>226</v>
+        <v>106</v>
       </c>
       <c r="N129" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="O129" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>107</v>
+      </c>
+      <c r="O129" s="2"/>
       <c r="P129" t="s" s="2">
         <v>75</v>
       </c>
@@ -16706,7 +16731,7 @@
         <v>75</v>
       </c>
       <c r="S129" t="s" s="2">
-        <v>229</v>
+        <v>75</v>
       </c>
       <c r="T129" t="s" s="2">
         <v>75</v>
@@ -16733,31 +16758,31 @@
         <v>75</v>
       </c>
       <c r="AB129" t="s" s="2">
-        <v>75</v>
+        <v>108</v>
       </c>
       <c r="AC129" t="s" s="2">
-        <v>75</v>
+        <v>109</v>
       </c>
       <c r="AD129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE129" t="s" s="2">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>230</v>
+        <v>111</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH129" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ129" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK129" t="s" s="2">
         <v>75</v>
@@ -16766,15 +16791,15 @@
         <v>75</v>
       </c>
       <c r="AM129" t="s" s="2">
-        <v>231</v>
+        <v>75</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -16782,7 +16807,7 @@
       </c>
       <c r="E130" s="2"/>
       <c r="F130" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>84</v>
@@ -16797,18 +16822,20 @@
         <v>85</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>236</v>
-      </c>
-      <c r="O130" s="2"/>
+        <v>227</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="P130" t="s" s="2">
         <v>75</v>
       </c>
@@ -16817,7 +16844,7 @@
         <v>75</v>
       </c>
       <c r="S130" t="s" s="2">
-        <v>75</v>
+        <v>229</v>
       </c>
       <c r="T130" t="s" s="2">
         <v>75</v>
@@ -16856,7 +16883,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -16877,15 +16904,15 @@
         <v>75</v>
       </c>
       <c r="AM130" t="s" s="2">
-        <v>238</v>
+        <v>231</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -16893,7 +16920,7 @@
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G131" t="s" s="2">
         <v>84</v>
@@ -16908,18 +16935,18 @@
         <v>85</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>159</v>
+        <v>98</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="N131" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="O131" s="2"/>
       <c r="P131" t="s" s="2">
         <v>75</v>
       </c>
@@ -16967,7 +16994,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -16988,15 +17015,15 @@
         <v>75</v>
       </c>
       <c r="AM131" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
     </row>
-    <row r="132" hidden="true">
+    <row r="132">
       <c r="A132" t="s" s="2">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17004,13 +17031,13 @@
       </c>
       <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G132" t="s" s="2">
         <v>84</v>
       </c>
       <c r="H132" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I132" t="s" s="2">
         <v>75</v>
@@ -17019,17 +17046,17 @@
         <v>85</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>98</v>
+        <v>159</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>75</v>
@@ -17078,7 +17105,7 @@
         <v>75</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17099,15 +17126,15 @@
         <v>75</v>
       </c>
       <c r="AM132" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17130,19 +17157,17 @@
         <v>85</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>255</v>
+        <v>98</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="N133" t="s" s="2">
-        <v>258</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>75</v>
@@ -17191,7 +17216,7 @@
         <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17212,15 +17237,15 @@
         <v>75</v>
       </c>
       <c r="AM133" t="s" s="2">
-        <v>261</v>
+        <v>252</v>
       </c>
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>611</v>
+        <v>616</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17243,19 +17268,19 @@
         <v>85</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>98</v>
+        <v>255</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>352</v>
+        <v>256</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>353</v>
+        <v>257</v>
       </c>
       <c r="N134" t="s" s="2">
-        <v>354</v>
+        <v>258</v>
       </c>
       <c r="O134" t="s" s="2">
-        <v>355</v>
+        <v>259</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>75</v>
@@ -17304,7 +17329,7 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>356</v>
+        <v>260</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17325,15 +17350,15 @@
         <v>75</v>
       </c>
       <c r="AM134" t="s" s="2">
-        <v>357</v>
+        <v>261</v>
       </c>
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>612</v>
+        <v>617</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17356,18 +17381,20 @@
         <v>85</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>308</v>
+        <v>98</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>613</v>
+        <v>352</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>614</v>
+        <v>353</v>
       </c>
       <c r="N135" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="O135" s="2"/>
+        <v>354</v>
+      </c>
+      <c r="O135" t="s" s="2">
+        <v>355</v>
+      </c>
       <c r="P135" t="s" s="2">
         <v>75</v>
       </c>
@@ -17391,13 +17418,13 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y135" t="s" s="2">
-        <v>616</v>
+        <v>75</v>
       </c>
       <c r="Z135" t="s" s="2">
-        <v>617</v>
+        <v>75</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -17415,7 +17442,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>612</v>
+        <v>356</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17436,7 +17463,7 @@
         <v>75</v>
       </c>
       <c r="AM135" t="s" s="2">
-        <v>75</v>
+        <v>357</v>
       </c>
     </row>
     <row r="136" hidden="true">
@@ -17455,7 +17482,7 @@
         <v>76</v>
       </c>
       <c r="G136" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H136" t="s" s="2">
         <v>75</v>
@@ -17464,19 +17491,19 @@
         <v>75</v>
       </c>
       <c r="J136" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K136" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L136" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L136" t="s" s="2">
+      <c r="M136" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M136" t="s" s="2">
+      <c r="N136" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N136" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O136" s="2"/>
       <c r="P136" t="s" s="2">
@@ -17502,13 +17529,13 @@
         <v>75</v>
       </c>
       <c r="X136" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y136" t="s" s="2">
-        <v>75</v>
+        <v>622</v>
       </c>
       <c r="Z136" t="s" s="2">
-        <v>75</v>
+        <v>623</v>
       </c>
       <c r="AA136" t="s" s="2">
         <v>75</v>
@@ -17532,7 +17559,7 @@
         <v>76</v>
       </c>
       <c r="AH136" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI136" t="s" s="2">
         <v>75</v>
@@ -17552,10 +17579,10 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17578,16 +17605,16 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>308</v>
+        <v>625</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="O137" s="2"/>
       <c r="P137" t="s" s="2">
@@ -17613,13 +17640,13 @@
         <v>75</v>
       </c>
       <c r="X137" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y137" t="s" s="2">
-        <v>627</v>
+        <v>75</v>
       </c>
       <c r="Z137" t="s" s="2">
-        <v>628</v>
+        <v>75</v>
       </c>
       <c r="AA137" t="s" s="2">
         <v>75</v>
@@ -17637,7 +17664,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -17689,18 +17716,18 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L138" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="L138" t="s" s="2">
+      <c r="M138" t="s" s="2">
         <v>631</v>
       </c>
-      <c r="M138" t="s" s="2">
+      <c r="N138" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="N138" s="2"/>
-      <c r="O138" t="s" s="2">
-        <v>633</v>
-      </c>
+      <c r="O138" s="2"/>
       <c r="P138" t="s" s="2">
         <v>75</v>
       </c>
@@ -17724,13 +17751,13 @@
         <v>75</v>
       </c>
       <c r="X138" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y138" t="s" s="2">
-        <v>75</v>
+        <v>633</v>
       </c>
       <c r="Z138" t="s" s="2">
-        <v>75</v>
+        <v>634</v>
       </c>
       <c r="AA138" t="s" s="2">
         <v>75</v>
@@ -17774,10 +17801,10 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -17800,16 +17827,18 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>308</v>
+        <v>636</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
+      <c r="O139" t="s" s="2">
+        <v>639</v>
+      </c>
       <c r="P139" t="s" s="2">
         <v>75</v>
       </c>
@@ -17833,13 +17862,13 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y139" t="s" s="2">
-        <v>637</v>
+        <v>75</v>
       </c>
       <c r="Z139" t="s" s="2">
-        <v>638</v>
+        <v>75</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>75</v>
@@ -17857,7 +17886,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -17881,12 +17910,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -17900,7 +17929,7 @@
         <v>77</v>
       </c>
       <c r="H140" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I140" t="s" s="2">
         <v>75</v>
@@ -17909,7 +17938,7 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>640</v>
+        <v>308</v>
       </c>
       <c r="L140" t="s" s="2">
         <v>641</v>
@@ -17942,13 +17971,13 @@
         <v>75</v>
       </c>
       <c r="X140" t="s" s="2">
-        <v>75</v>
+        <v>149</v>
       </c>
       <c r="Y140" t="s" s="2">
-        <v>75</v>
+        <v>643</v>
       </c>
       <c r="Z140" t="s" s="2">
-        <v>75</v>
+        <v>644</v>
       </c>
       <c r="AA140" t="s" s="2">
         <v>75</v>
@@ -17966,7 +17995,7 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -17981,16 +18010,16 @@
         <v>96</v>
       </c>
       <c r="AK140" t="s" s="2">
-        <v>643</v>
+        <v>75</v>
       </c>
       <c r="AL140" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM140" t="s" s="2">
-        <v>644</v>
+        <v>75</v>
       </c>
     </row>
-    <row r="141" hidden="true">
+    <row r="141">
       <c r="A141" t="s" s="2">
         <v>645</v>
       </c>
@@ -18009,7 +18038,7 @@
         <v>77</v>
       </c>
       <c r="H141" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I141" t="s" s="2">
         <v>75</v>
@@ -18018,13 +18047,13 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>532</v>
+        <v>646</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18090,21 +18119,21 @@
         <v>96</v>
       </c>
       <c r="AK141" t="s" s="2">
-        <v>75</v>
+        <v>649</v>
       </c>
       <c r="AL141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AM141" t="s" s="2">
-        <v>75</v>
+        <v>650</v>
       </c>
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18115,7 +18144,7 @@
         <v>76</v>
       </c>
       <c r="G142" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H142" t="s" s="2">
         <v>75</v>
@@ -18127,13 +18156,13 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>98</v>
+        <v>533</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>99</v>
+        <v>652</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>100</v>
+        <v>653</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18184,19 +18213,19 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>101</v>
+        <v>651</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH142" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ142" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AK142" t="s" s="2">
         <v>75</v>
@@ -18210,21 +18239,21 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>649</v>
+        <v>654</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G143" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H143" t="s" s="2">
         <v>75</v>
@@ -18236,17 +18265,15 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="N143" t="s" s="2">
-        <v>107</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="N143" s="2"/>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
         <v>75</v>
@@ -18295,19 +18322,19 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH143" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ143" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AK143" t="s" s="2">
         <v>75</v>
@@ -18321,14 +18348,14 @@
     </row>
     <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>650</v>
+        <v>655</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>539</v>
+        <v>103</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18341,26 +18368,24 @@
         <v>75</v>
       </c>
       <c r="I144" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J144" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
         <v>104</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>540</v>
+        <v>105</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>541</v>
+        <v>106</v>
       </c>
       <c r="N144" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="O144" t="s" s="2">
-        <v>265</v>
-      </c>
+      <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
         <v>75</v>
       </c>
@@ -18408,7 +18433,7 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>542</v>
+        <v>111</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18434,42 +18459,46 @@
     </row>
     <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>651</v>
+        <v>656</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
-        <v>75</v>
+        <v>540</v>
       </c>
       <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G145" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I145" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J145" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>308</v>
+        <v>104</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>652</v>
+        <v>541</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>653</v>
-      </c>
-      <c r="N145" s="2"/>
-      <c r="O145" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N145" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="O145" t="s" s="2">
+        <v>265</v>
+      </c>
       <c r="P145" t="s" s="2">
         <v>75</v>
       </c>
@@ -18493,13 +18522,13 @@
         <v>75</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>163</v>
+        <v>75</v>
       </c>
       <c r="Y145" t="s" s="2">
-        <v>654</v>
+        <v>75</v>
       </c>
       <c r="Z145" t="s" s="2">
-        <v>655</v>
+        <v>75</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>75</v>
@@ -18517,19 +18546,19 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>651</v>
+        <v>543</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH145" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI145" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ145" t="s" s="2">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="AK145" t="s" s="2">
         <v>75</v>
@@ -18543,10 +18572,10 @@
     </row>
     <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18554,7 +18583,7 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>84</v>
@@ -18569,7 +18598,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>657</v>
+        <v>308</v>
       </c>
       <c r="L146" t="s" s="2">
         <v>658</v>
@@ -18602,13 +18631,13 @@
         <v>75</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>75</v>
+        <v>163</v>
       </c>
       <c r="Y146" t="s" s="2">
-        <v>75</v>
+        <v>660</v>
       </c>
       <c r="Z146" t="s" s="2">
-        <v>75</v>
+        <v>661</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>75</v>
@@ -18626,10 +18655,10 @@
         <v>75</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>84</v>
@@ -18652,10 +18681,10 @@
     </row>
     <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -18663,10 +18692,10 @@
       </c>
       <c r="E147" s="2"/>
       <c r="F147" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G147" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H147" t="s" s="2">
         <v>75</v>
@@ -18678,20 +18707,16 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>663</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O147" t="s" s="2">
         <v>665</v>
       </c>
+      <c r="N147" s="2"/>
+      <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
         <v>75</v>
       </c>
@@ -18739,13 +18764,13 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="AH147" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI147" t="s" s="2">
         <v>75</v>
@@ -18791,18 +18816,20 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>308</v>
+        <v>667</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N148" t="s" s="2">
-        <v>664</v>
-      </c>
-      <c r="O148" s="2"/>
+        <v>670</v>
+      </c>
+      <c r="O148" t="s" s="2">
+        <v>671</v>
+      </c>
       <c r="P148" t="s" s="2">
         <v>75</v>
       </c>
@@ -18826,13 +18853,13 @@
         <v>75</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>149</v>
+        <v>75</v>
       </c>
       <c r="Y148" t="s" s="2">
-        <v>669</v>
+        <v>75</v>
       </c>
       <c r="Z148" t="s" s="2">
-        <v>670</v>
+        <v>75</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>75</v>
@@ -18874,8 +18901,119 @@
         <v>75</v>
       </c>
     </row>
+    <row r="149" hidden="true">
+      <c r="A149" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="B149" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="C149" s="2"/>
+      <c r="D149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E149" s="2"/>
+      <c r="F149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K149" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="L149" t="s" s="2">
+        <v>673</v>
+      </c>
+      <c r="M149" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="N149" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O149" s="2"/>
+      <c r="P149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q149" s="2"/>
+      <c r="R149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X149" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="Y149" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="Z149" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="AA149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF149" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AG149" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH149" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ149" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AK149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AL149" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AM149" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AM148">
+  <autoFilter ref="A1:AM149">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -18885,7 +19023,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI147">
+  <conditionalFormatting sqref="A2:AI148">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
